--- a/selenium_model/APPIUM_END_TO_END_ADVANCED_REPORT.xlsx
+++ b/selenium_model/APPIUM_END_TO_END_ADVANCED_REPORT.xlsx
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -14561,7 +14561,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
